--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/169.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/169.xlsx
@@ -426,13 +426,13 @@
         <v>-16.50674155548771</v>
       </c>
       <c r="E2">
-        <v>-4.926968211630927</v>
+        <v>-5.368462728060734</v>
       </c>
       <c r="F2">
-        <v>-5.947041084815205</v>
+        <v>-4.987756012575058</v>
       </c>
       <c r="G2">
-        <v>-0.9322176690717074</v>
+        <v>-4.103885822970469</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-16.58500319733601</v>
       </c>
       <c r="E3">
-        <v>-5.109175891803552</v>
+        <v>-6.218018037321716</v>
       </c>
       <c r="F3">
-        <v>-5.134435856956169</v>
+        <v>-5.055538832043933</v>
       </c>
       <c r="G3">
-        <v>-2.116379945195776</v>
+        <v>-4.356996892720986</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.46555850041536</v>
       </c>
       <c r="E4">
-        <v>-4.871648373153227</v>
+        <v>-6.560207647237319</v>
       </c>
       <c r="F4">
-        <v>-5.110910222716663</v>
+        <v>-4.808976102968063</v>
       </c>
       <c r="G4">
-        <v>-2.337898478865029</v>
+        <v>-4.022843668169109</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.14809666911055</v>
       </c>
       <c r="E5">
-        <v>-8.197269114906184</v>
+        <v>-7.918052464541245</v>
       </c>
       <c r="F5">
-        <v>-5.207135865328062</v>
+        <v>-4.453787899628288</v>
       </c>
       <c r="G5">
-        <v>-2.372506921932569</v>
+        <v>-2.899082295409044</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-15.66292630191069</v>
       </c>
       <c r="E6">
-        <v>-9.43910348508161</v>
+        <v>-8.931647216256078</v>
       </c>
       <c r="F6">
-        <v>-5.550571191956917</v>
+        <v>-4.685554330155353</v>
       </c>
       <c r="G6">
-        <v>-1.621281238706691</v>
+        <v>-4.595673983920282</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.02291624453314</v>
       </c>
       <c r="E7">
-        <v>-7.900142349840909</v>
+        <v>-10.28688816100559</v>
       </c>
       <c r="F7">
-        <v>-5.491220324281138</v>
+        <v>-4.823335023528189</v>
       </c>
       <c r="G7">
-        <v>-2.270267344043257</v>
+        <v>-4.39926924871194</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.26707984430626</v>
       </c>
       <c r="E8">
-        <v>-9.497806093643041</v>
+        <v>-11.23170444949193</v>
       </c>
       <c r="F8">
-        <v>-5.000086261365728</v>
+        <v>-4.6168014924578</v>
       </c>
       <c r="G8">
-        <v>-1.492140167765261</v>
+        <v>-4.418410823020006</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.42664915232467</v>
       </c>
       <c r="E9">
-        <v>-12.1764256400241</v>
+        <v>-11.90218125411959</v>
       </c>
       <c r="F9">
-        <v>-5.659355712762159</v>
+        <v>-4.765387410232752</v>
       </c>
       <c r="G9">
-        <v>-1.342966985765701</v>
+        <v>-3.648861270234261</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.5162285481974</v>
       </c>
       <c r="E10">
-        <v>-11.79843844307787</v>
+        <v>-13.28558930719681</v>
       </c>
       <c r="F10">
-        <v>-4.810548344298576</v>
+        <v>-4.682234233604932</v>
       </c>
       <c r="G10">
-        <v>-1.582104242794956</v>
+        <v>-2.601808548164649</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.57574583640747</v>
       </c>
       <c r="E11">
-        <v>-13.02474014740698</v>
+        <v>-15.23724386417854</v>
       </c>
       <c r="F11">
-        <v>-5.366300863204167</v>
+        <v>-4.81987327615189</v>
       </c>
       <c r="G11">
-        <v>-0.9329029519983366</v>
+        <v>-3.140715703774909</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.63337789705907</v>
       </c>
       <c r="E12">
-        <v>-13.59078128446975</v>
+        <v>-14.41864520323399</v>
       </c>
       <c r="F12">
-        <v>-4.777107980614963</v>
+        <v>-4.618301665824269</v>
       </c>
       <c r="G12">
-        <v>-0.1453307892967998</v>
+        <v>-2.364065030807428</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.703453778148191</v>
       </c>
       <c r="E13">
-        <v>-13.93646234784526</v>
+        <v>-15.95006190077791</v>
       </c>
       <c r="F13">
-        <v>-4.826734643349278</v>
+        <v>-4.63677177380449</v>
       </c>
       <c r="G13">
-        <v>-0.3675710218936138</v>
+        <v>-1.541487159573637</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.83042684672561</v>
       </c>
       <c r="E14">
-        <v>-16.29880421258261</v>
+        <v>-17.03899234608435</v>
       </c>
       <c r="F14">
-        <v>-5.051479831770215</v>
+        <v>-4.779723964873003</v>
       </c>
       <c r="G14">
-        <v>0.7422032959630306</v>
+        <v>-0.5142248787377881</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.037776725759571</v>
       </c>
       <c r="E15">
-        <v>-18.23511177115234</v>
+        <v>-18.40304570125279</v>
       </c>
       <c r="F15">
-        <v>-5.028028750596961</v>
+        <v>-4.914697321117752</v>
       </c>
       <c r="G15">
-        <v>0.7367309641866153</v>
+        <v>0.4240300747292161</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.336510287981039</v>
       </c>
       <c r="E16">
-        <v>-18.41247398413676</v>
+        <v>-19.07569617340413</v>
       </c>
       <c r="F16">
-        <v>-4.966678204010824</v>
+        <v>-4.773203885045569</v>
       </c>
       <c r="G16">
-        <v>2.784995284243552</v>
+        <v>0.5956421343939559</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.754039581095785</v>
       </c>
       <c r="E17">
-        <v>-18.20652351474192</v>
+        <v>-20.16746597191338</v>
       </c>
       <c r="F17">
-        <v>-4.813143619371547</v>
+        <v>-4.209376440697488</v>
       </c>
       <c r="G17">
-        <v>3.474552125163887</v>
+        <v>1.302218489931684</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.289916473158015</v>
       </c>
       <c r="E18">
-        <v>-19.19238589163378</v>
+        <v>-21.25401443989178</v>
       </c>
       <c r="F18">
-        <v>-4.86083438748552</v>
+        <v>-4.263312270661166</v>
       </c>
       <c r="G18">
-        <v>3.735413182021839</v>
+        <v>1.474138430331576</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-5.932140002983746</v>
       </c>
       <c r="E19">
-        <v>-20.69163683830122</v>
+        <v>-22.05993337361485</v>
       </c>
       <c r="F19">
-        <v>-5.116245737158095</v>
+        <v>-4.53160059161026</v>
       </c>
       <c r="G19">
-        <v>3.929142996434449</v>
+        <v>2.606947524050469</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-5.680788272439433</v>
       </c>
       <c r="E20">
-        <v>-19.66799340276337</v>
+        <v>-22.59643527472558</v>
       </c>
       <c r="F20">
-        <v>-4.512789196260085</v>
+        <v>-3.887098445903534</v>
       </c>
       <c r="G20">
-        <v>4.76257945703705</v>
+        <v>3.282361714427037</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-5.51464405156918</v>
       </c>
       <c r="E21">
-        <v>-21.79595503828572</v>
+        <v>-23.1139809836402</v>
       </c>
       <c r="F21">
-        <v>-4.882563292828354</v>
+        <v>-4.015746388660506</v>
       </c>
       <c r="G21">
-        <v>4.248067711505678</v>
+        <v>3.659979091364006</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-5.412236071103496</v>
       </c>
       <c r="E22">
-        <v>-21.46560285942617</v>
+        <v>-24.00333252248059</v>
       </c>
       <c r="F22">
-        <v>-4.138442511628363</v>
+        <v>-3.938126706283387</v>
       </c>
       <c r="G22">
-        <v>5.092700437122094</v>
+        <v>3.205937770652962</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-5.364590978985389</v>
       </c>
       <c r="E23">
-        <v>-23.50367428589627</v>
+        <v>-25.08609971466259</v>
       </c>
       <c r="F23">
-        <v>-4.248467098435596</v>
+        <v>-3.800943265807969</v>
       </c>
       <c r="G23">
-        <v>4.983081653225746</v>
+        <v>4.714003822339323</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.351045213610307</v>
       </c>
       <c r="E24">
-        <v>-23.2805246722203</v>
+        <v>-24.82141946586227</v>
       </c>
       <c r="F24">
-        <v>-3.907352028901983</v>
+        <v>-3.488539410455386</v>
       </c>
       <c r="G24">
-        <v>4.471443461222463</v>
+        <v>4.195919998171079</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.357515004228184</v>
       </c>
       <c r="E25">
-        <v>-23.21003897429091</v>
+        <v>-25.08104140919602</v>
       </c>
       <c r="F25">
-        <v>-3.426817755272795</v>
+        <v>-3.745576845339656</v>
       </c>
       <c r="G25">
-        <v>4.427671428102219</v>
+        <v>4.014323333159897</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.381127016574682</v>
       </c>
       <c r="E26">
-        <v>-22.87505869499552</v>
+        <v>-25.43091131102863</v>
       </c>
       <c r="F26">
-        <v>-3.578076814656582</v>
+        <v>-3.760672184520871</v>
       </c>
       <c r="G26">
-        <v>4.925809215396354</v>
+        <v>4.383455781879713</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.412064953743731</v>
       </c>
       <c r="E27">
-        <v>-22.59060712867771</v>
+        <v>-25.30776398886405</v>
       </c>
       <c r="F27">
-        <v>-3.937411825214771</v>
+        <v>-3.871491175667389</v>
       </c>
       <c r="G27">
-        <v>4.50838252834965</v>
+        <v>4.338938876013133</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.448861827239402</v>
       </c>
       <c r="E28">
-        <v>-24.04690097090839</v>
+        <v>-25.60642137814391</v>
       </c>
       <c r="F28">
-        <v>-2.88693592743744</v>
+        <v>-3.428497684365672</v>
       </c>
       <c r="G28">
-        <v>3.56547625839997</v>
+        <v>3.968737121084133</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.499350048553291</v>
       </c>
       <c r="E29">
-        <v>-22.87058909114995</v>
+        <v>-24.87956054364675</v>
       </c>
       <c r="F29">
-        <v>-3.961131297426532</v>
+        <v>-3.498391183976881</v>
       </c>
       <c r="G29">
-        <v>4.92646470341313</v>
+        <v>3.467560252984946</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.563862890864692</v>
       </c>
       <c r="E30">
-        <v>-23.22076692921508</v>
+        <v>-23.35980466667258</v>
       </c>
       <c r="F30">
-        <v>-3.691703142931187</v>
+        <v>-3.514588251803819</v>
       </c>
       <c r="G30">
-        <v>3.857936472430265</v>
+        <v>4.63997671353568</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.650684289302841</v>
       </c>
       <c r="E31">
-        <v>-23.34880500330795</v>
+        <v>-24.30440811688056</v>
       </c>
       <c r="F31">
-        <v>-3.485388300855137</v>
+        <v>-3.352691298233281</v>
       </c>
       <c r="G31">
-        <v>3.735118543468844</v>
+        <v>3.784028543266036</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.773369395236487</v>
       </c>
       <c r="E32">
-        <v>-23.50498754335849</v>
+        <v>-23.48489017571245</v>
       </c>
       <c r="F32">
-        <v>-3.63668463677205</v>
+        <v>-3.581091243635369</v>
       </c>
       <c r="G32">
-        <v>4.840618947034289</v>
+        <v>3.565330594396242</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.933000999641536</v>
       </c>
       <c r="E33">
-        <v>-20.63873973341762</v>
+        <v>-23.57981604786124</v>
       </c>
       <c r="F33">
-        <v>-3.087390898506087</v>
+        <v>-3.711487041612248</v>
       </c>
       <c r="G33">
-        <v>4.342967809934426</v>
+        <v>3.073933077820063</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.138162862553659</v>
       </c>
       <c r="E34">
-        <v>-23.1342911895646</v>
+        <v>-23.54156402791845</v>
       </c>
       <c r="F34">
-        <v>-4.25534751808325</v>
+        <v>-3.861843180526983</v>
       </c>
       <c r="G34">
-        <v>4.21417434627462</v>
+        <v>4.007275181706788</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.395969174649427</v>
       </c>
       <c r="E35">
-        <v>-20.35127220341071</v>
+        <v>-22.37494308253642</v>
       </c>
       <c r="F35">
-        <v>-3.428154740260913</v>
+        <v>-3.480841392181171</v>
       </c>
       <c r="G35">
-        <v>4.403481271846764</v>
+        <v>3.507518537643949</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.696862649211253</v>
       </c>
       <c r="E36">
-        <v>-19.55512118812219</v>
+        <v>-22.21453547623672</v>
       </c>
       <c r="F36">
-        <v>-3.207244064547536</v>
+        <v>-3.621395459618579</v>
       </c>
       <c r="G36">
-        <v>3.266947814396191</v>
+        <v>2.691346572028649</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.04169449698629</v>
       </c>
       <c r="E37">
-        <v>-20.55427916470056</v>
+        <v>-21.57034193474958</v>
       </c>
       <c r="F37">
-        <v>-3.379611582089459</v>
+        <v>-3.506548117792248</v>
       </c>
       <c r="G37">
-        <v>2.881580450351789</v>
+        <v>2.606143061484426</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.426841686282658</v>
       </c>
       <c r="E38">
-        <v>-19.58055762662327</v>
+        <v>-19.3762419363452</v>
       </c>
       <c r="F38">
-        <v>-3.066144102991682</v>
+        <v>-3.652215697207138</v>
       </c>
       <c r="G38">
-        <v>4.363880526106002</v>
+        <v>2.446882647226707</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-7.833079235449657</v>
       </c>
       <c r="E39">
-        <v>-18.85289072375274</v>
+        <v>-18.32514689137285</v>
       </c>
       <c r="F39">
-        <v>-3.346070157582705</v>
+        <v>-3.544537046884633</v>
       </c>
       <c r="G39">
-        <v>3.219567286638142</v>
+        <v>2.139650779000184</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.25837630554433</v>
       </c>
       <c r="E40">
-        <v>-17.1291723774731</v>
+        <v>-19.12731172014356</v>
       </c>
       <c r="F40">
-        <v>-3.277045615377033</v>
+        <v>-3.455232413923623</v>
       </c>
       <c r="G40">
-        <v>2.733188557099497</v>
+        <v>1.56982643859867</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.695081606715016</v>
       </c>
       <c r="E41">
-        <v>-17.15102226456011</v>
+        <v>-18.63900636789646</v>
       </c>
       <c r="F41">
-        <v>-3.063594388125865</v>
+        <v>-3.228243178208503</v>
       </c>
       <c r="G41">
-        <v>2.429889616973628</v>
+        <v>0.5942318419942263</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.122493760204069</v>
       </c>
       <c r="E42">
-        <v>-15.93548474294722</v>
+        <v>-16.76675407416523</v>
       </c>
       <c r="F42">
-        <v>-3.355946782126283</v>
+        <v>-3.750623259557511</v>
       </c>
       <c r="G42">
-        <v>1.903532739502745</v>
+        <v>1.46339902060218</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.541946656568387</v>
       </c>
       <c r="E43">
-        <v>-15.76625114080657</v>
+        <v>-15.66943689499659</v>
       </c>
       <c r="F43">
-        <v>-2.717431247639591</v>
+        <v>-3.270101411439365</v>
       </c>
       <c r="G43">
-        <v>1.129590092786388</v>
+        <v>1.284689151301243</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.945454821188893</v>
       </c>
       <c r="E44">
-        <v>-14.78218203962175</v>
+        <v>-15.39149727430181</v>
       </c>
       <c r="F44">
-        <v>-2.651880049953857</v>
+        <v>-3.023339874186823</v>
       </c>
       <c r="G44">
-        <v>1.048458553255469</v>
+        <v>-0.4988771896177269</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-10.31486631611842</v>
       </c>
       <c r="E45">
-        <v>-13.04466090456673</v>
+        <v>-14.01379509847425</v>
       </c>
       <c r="F45">
-        <v>-2.941269373754462</v>
+        <v>-2.954559700364977</v>
       </c>
       <c r="G45">
-        <v>1.40594119222259</v>
+        <v>-0.4127235525037335</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-10.6544593590243</v>
       </c>
       <c r="E46">
-        <v>-13.13773010237237</v>
+        <v>-12.77579181730931</v>
       </c>
       <c r="F46">
-        <v>-3.065103673533766</v>
+        <v>-2.849762111869409</v>
       </c>
       <c r="G46">
-        <v>0.07476752033610584</v>
+        <v>-0.1719310227048438</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.95685348655016</v>
       </c>
       <c r="E47">
-        <v>-11.41142599743434</v>
+        <v>-12.40996810154768</v>
       </c>
       <c r="F47">
-        <v>-2.644236703928227</v>
+        <v>-2.987309205634656</v>
       </c>
       <c r="G47">
-        <v>-0.660580786483428</v>
+        <v>-1.305749832813215</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.21101700501285</v>
       </c>
       <c r="E48">
-        <v>-9.330211799093169</v>
+        <v>-12.07576671978161</v>
       </c>
       <c r="F48">
-        <v>-2.684593935425216</v>
+        <v>-2.982974359015806</v>
       </c>
       <c r="G48">
-        <v>0.3723160428602609</v>
+        <v>-1.503962125885999</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-11.42569679857253</v>
       </c>
       <c r="E49">
-        <v>-9.02943961245172</v>
+        <v>-11.43865571164246</v>
       </c>
       <c r="F49">
-        <v>-2.33369004829272</v>
+        <v>-2.472816838695105</v>
       </c>
       <c r="G49">
-        <v>-0.1299698579945814</v>
+        <v>-1.040502303115729</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-11.59671709805105</v>
       </c>
       <c r="E50">
-        <v>-9.104331515590571</v>
+        <v>-10.72169864980008</v>
       </c>
       <c r="F50">
-        <v>-2.558586827948369</v>
+        <v>-3.078926640384281</v>
       </c>
       <c r="G50">
-        <v>0.008546677914064292</v>
+        <v>-1.535190501957944</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-11.72079087058057</v>
       </c>
       <c r="E51">
-        <v>-6.873578048568108</v>
+        <v>-8.710068983060767</v>
       </c>
       <c r="F51">
-        <v>-2.630876794455876</v>
+        <v>-2.62470545730502</v>
       </c>
       <c r="G51">
-        <v>-2.1514253802745</v>
+        <v>-2.640234050238969</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-11.80883963934495</v>
       </c>
       <c r="E52">
-        <v>-8.251289281343684</v>
+        <v>-7.916444856268522</v>
       </c>
       <c r="F52">
-        <v>-2.331548718556483</v>
+        <v>-2.142516933972441</v>
       </c>
       <c r="G52">
-        <v>-2.635682050122472</v>
+        <v>-2.815951186372406</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-11.85596451558591</v>
       </c>
       <c r="E53">
-        <v>-7.270747861410836</v>
+        <v>-7.731637832015495</v>
       </c>
       <c r="F53">
-        <v>-2.516375710203914</v>
+        <v>-2.670665765914545</v>
       </c>
       <c r="G53">
-        <v>-1.874230091725785</v>
+        <v>-3.32781449547236</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-11.86320341564725</v>
       </c>
       <c r="E54">
-        <v>-5.92260303543134</v>
+        <v>-7.886892034894466</v>
       </c>
       <c r="F54">
-        <v>-2.550268362489456</v>
+        <v>-2.473828275293923</v>
       </c>
       <c r="G54">
-        <v>-1.747237564839342</v>
+        <v>-4.564015236928231</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-11.83974255397976</v>
       </c>
       <c r="E55">
-        <v>-4.273858104822686</v>
+        <v>-7.711386496253193</v>
       </c>
       <c r="F55">
-        <v>-1.974895133281156</v>
+        <v>-2.377536363290301</v>
       </c>
       <c r="G55">
-        <v>-2.184961206587317</v>
+        <v>-3.222668258599567</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-11.77844835273438</v>
       </c>
       <c r="E56">
-        <v>-4.709157668809999</v>
+        <v>-6.456609747363844</v>
       </c>
       <c r="F56">
-        <v>-2.552437856717388</v>
+        <v>-2.699445734590008</v>
       </c>
       <c r="G56">
-        <v>-2.97695956867486</v>
+        <v>-3.882142172204545</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-11.68520319907545</v>
       </c>
       <c r="E57">
-        <v>-3.108025113917991</v>
+        <v>-5.87913874190572</v>
       </c>
       <c r="F57">
-        <v>-2.701600318204689</v>
+        <v>-2.436160752753824</v>
       </c>
       <c r="G57">
-        <v>-2.815676411092646</v>
+        <v>-3.960320705114434</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-11.5690368064427</v>
       </c>
       <c r="E58">
-        <v>-4.231820280609482</v>
+        <v>-4.107921231759621</v>
       </c>
       <c r="F58">
-        <v>-2.408489139663307</v>
+        <v>-2.38864145669223</v>
       </c>
       <c r="G58">
-        <v>-3.893050419756444</v>
+        <v>-4.143622301078341</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-11.4228407931251</v>
       </c>
       <c r="E59">
-        <v>-2.104225451481748</v>
+        <v>-4.759210892016779</v>
       </c>
       <c r="F59">
-        <v>-2.130866774819469</v>
+        <v>-2.958442258381898</v>
       </c>
       <c r="G59">
-        <v>-3.553828749983943</v>
+        <v>-4.980336201764819</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-11.25807420811971</v>
       </c>
       <c r="E60">
-        <v>-1.872372110763034</v>
+        <v>-4.21621515917905</v>
       </c>
       <c r="F60">
-        <v>-2.638319675570029</v>
+        <v>-2.555438203450328</v>
       </c>
       <c r="G60">
-        <v>-2.747131565702036</v>
+        <v>-4.619996561997307</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.08179592580831</v>
       </c>
       <c r="E61">
-        <v>-3.848937803260953</v>
+        <v>-3.914777286858472</v>
       </c>
       <c r="F61">
-        <v>-2.491185057484782</v>
+        <v>-2.76651450135767</v>
       </c>
       <c r="G61">
-        <v>-3.20907515861532</v>
+        <v>-4.843183610618353</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.88466666814394</v>
       </c>
       <c r="E62">
-        <v>0.1538799985470445</v>
+        <v>-3.427445556523027</v>
       </c>
       <c r="F62">
-        <v>-2.728055887947897</v>
+        <v>-2.433852921169625</v>
       </c>
       <c r="G62">
-        <v>-3.856571518459214</v>
+        <v>-4.371566603639319</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.67978906416648</v>
       </c>
       <c r="E63">
-        <v>-2.251640865853442</v>
+        <v>-3.351294737610042</v>
       </c>
       <c r="F63">
-        <v>-3.269571256301573</v>
+        <v>-2.44486772252465</v>
       </c>
       <c r="G63">
-        <v>-4.283943084305889</v>
+        <v>-4.723831822836548</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.46929515630861</v>
       </c>
       <c r="E64">
-        <v>-0.730784569695406</v>
+        <v>-1.982169491553009</v>
       </c>
       <c r="F64">
-        <v>-2.830728714055285</v>
+        <v>-2.775378032567624</v>
       </c>
       <c r="G64">
-        <v>-3.944416844343775</v>
+        <v>-4.727473422929746</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.24271265837182</v>
       </c>
       <c r="E65">
-        <v>-0.7107143728934109</v>
+        <v>-2.472394916779356</v>
       </c>
       <c r="F65">
-        <v>-3.00486313926738</v>
+        <v>-2.471734162499646</v>
       </c>
       <c r="G65">
-        <v>-3.773586073426303</v>
+        <v>-5.119018264950428</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.01219146330184</v>
       </c>
       <c r="E66">
-        <v>0.1422146495032856</v>
+        <v>-2.284227764812638</v>
       </c>
       <c r="F66">
-        <v>-2.897469447331438</v>
+        <v>-2.513845876155765</v>
       </c>
       <c r="G66">
-        <v>-3.498502912931643</v>
+        <v>-4.4041721666556</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.774569308784587</v>
       </c>
       <c r="E67">
-        <v>-0.02770728068652921</v>
+        <v>-2.518472139807402</v>
       </c>
       <c r="F67">
-        <v>-2.926270953559374</v>
+        <v>-2.973883026770081</v>
       </c>
       <c r="G67">
-        <v>-2.264235530070705</v>
+        <v>-4.477590135080018</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.518756462560907</v>
       </c>
       <c r="E68">
-        <v>0.4636185637236815</v>
+        <v>-2.435492382090851</v>
       </c>
       <c r="F68">
-        <v>-2.950160241088709</v>
+        <v>-2.723328395180121</v>
       </c>
       <c r="G68">
-        <v>-1.898949935267523</v>
+        <v>-4.05599878174491</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.251940357741379</v>
       </c>
       <c r="E69">
-        <v>0.6156983063232752</v>
+        <v>-2.528529880578438</v>
       </c>
       <c r="F69">
-        <v>-2.855783514520359</v>
+        <v>-2.634075120998085</v>
       </c>
       <c r="G69">
-        <v>-3.137885187338832</v>
+        <v>-4.188735105141989</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.964569400960164</v>
       </c>
       <c r="E70">
-        <v>-1.060090671059187</v>
+        <v>-1.396714786419363</v>
       </c>
       <c r="F70">
-        <v>-3.002545367274347</v>
+        <v>-2.687973674428637</v>
       </c>
       <c r="G70">
-        <v>-3.663593197884018</v>
+        <v>-4.275812384461439</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.646226769683302</v>
       </c>
       <c r="E71">
-        <v>-0.5388768981983515</v>
+        <v>-1.804368016589848</v>
       </c>
       <c r="F71">
-        <v>-2.627795267717462</v>
+        <v>-2.90860767542948</v>
       </c>
       <c r="G71">
-        <v>-2.434318117696302</v>
+        <v>-3.304663850516236</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.299387257156008</v>
       </c>
       <c r="E72">
-        <v>-1.237910259918378</v>
+        <v>-2.688181231718857</v>
       </c>
       <c r="F72">
-        <v>-2.984805050975993</v>
+        <v>-2.743965512286064</v>
       </c>
       <c r="G72">
-        <v>-2.302028717947025</v>
+        <v>-3.332419464317486</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.914012100791352</v>
       </c>
       <c r="E73">
-        <v>-2.028599935553653</v>
+        <v>-2.387630940303783</v>
       </c>
       <c r="F73">
-        <v>-3.467045761454947</v>
+        <v>-2.698680323109821</v>
       </c>
       <c r="G73">
-        <v>-1.329579139604889</v>
+        <v>-2.65181433853534</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.486446114543501</v>
       </c>
       <c r="E74">
-        <v>0.1028712673246455</v>
+        <v>-2.921442927853957</v>
       </c>
       <c r="F74">
-        <v>-3.441091353990433</v>
+        <v>-2.658924486347265</v>
       </c>
       <c r="G74">
-        <v>-2.076491181993097</v>
+        <v>-2.35760615646031</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.022249836802355</v>
       </c>
       <c r="E75">
-        <v>-2.815426822860386</v>
+        <v>-2.810603998042217</v>
       </c>
       <c r="F75">
-        <v>-3.421649571046729</v>
+        <v>-2.235807670875722</v>
       </c>
       <c r="G75">
-        <v>-1.824168022080926</v>
+        <v>-2.156460720039732</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.518864950407742</v>
       </c>
       <c r="E76">
-        <v>-0.8310495126992353</v>
+        <v>-4.64022523746524</v>
       </c>
       <c r="F76">
-        <v>-3.284769313040736</v>
+        <v>-2.736011528484384</v>
       </c>
       <c r="G76">
-        <v>-0.3807436825943739</v>
+        <v>-1.604827827376513</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.985127064484812</v>
       </c>
       <c r="E77">
-        <v>-3.910362024700994</v>
+        <v>-3.508260703663912</v>
       </c>
       <c r="F77">
-        <v>-3.23639431345205</v>
+        <v>-2.990678175861841</v>
       </c>
       <c r="G77">
-        <v>-0.9931482597219937</v>
+        <v>-1.433738833906978</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.435084469075717</v>
       </c>
       <c r="E78">
-        <v>-2.920052686333602</v>
+        <v>-5.786191812898286</v>
       </c>
       <c r="F78">
-        <v>-3.579105646970859</v>
+        <v>-3.400034980405481</v>
       </c>
       <c r="G78">
-        <v>-0.1018368420018549</v>
+        <v>-1.10222742469544</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.87563618033744</v>
       </c>
       <c r="E79">
-        <v>-3.43949129738343</v>
+        <v>-4.987776560605925</v>
       </c>
       <c r="F79">
-        <v>-3.441849310163995</v>
+        <v>-3.488888981499367</v>
       </c>
       <c r="G79">
-        <v>0.7789006932658517</v>
+        <v>-1.233033700043123</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.325099850819468</v>
       </c>
       <c r="E80">
-        <v>-3.616599915823418</v>
+        <v>-5.401371148674475</v>
       </c>
       <c r="F80">
-        <v>-3.615674754334846</v>
+        <v>-2.837478251653295</v>
       </c>
       <c r="G80">
-        <v>2.331218807175651</v>
+        <v>-0.1471184838880062</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.801587290585895</v>
       </c>
       <c r="E81">
-        <v>-5.433817664939433</v>
+        <v>-5.822052798565028</v>
       </c>
       <c r="F81">
-        <v>-4.158550301963919</v>
+        <v>-3.423702265470866</v>
       </c>
       <c r="G81">
-        <v>2.042449851421643</v>
+        <v>-0.124666364040669</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.315507760681263</v>
       </c>
       <c r="E82">
-        <v>-5.654943050733976</v>
+        <v>-7.909855926587362</v>
       </c>
       <c r="F82">
-        <v>-3.665329581560857</v>
+        <v>-2.887024562749539</v>
       </c>
       <c r="G82">
-        <v>1.635534146462125</v>
+        <v>0.816601185867072</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.887442140166855</v>
       </c>
       <c r="E83">
-        <v>-8.394982290081071</v>
+        <v>-7.989081579351555</v>
       </c>
       <c r="F83">
-        <v>-4.147321781818971</v>
+        <v>-3.585588450265168</v>
       </c>
       <c r="G83">
-        <v>3.269573077008833</v>
+        <v>1.821212714123228</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.53405448235471</v>
       </c>
       <c r="E84">
-        <v>-7.905825584720535</v>
+        <v>-9.963133968775217</v>
       </c>
       <c r="F84">
-        <v>-3.769180346115025</v>
+        <v>-3.690931932879181</v>
       </c>
       <c r="G84">
-        <v>1.63896387164081</v>
+        <v>1.345904448867906</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.261829794622423</v>
       </c>
       <c r="E85">
-        <v>-9.675290575425667</v>
+        <v>-10.30704439881374</v>
       </c>
       <c r="F85">
-        <v>-4.291172751519523</v>
+        <v>-3.787419339589865</v>
       </c>
       <c r="G85">
-        <v>3.201855868003041</v>
+        <v>2.504022663234528</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.086275383497242</v>
       </c>
       <c r="E86">
-        <v>-12.50541927668136</v>
+        <v>-11.73003584319201</v>
       </c>
       <c r="F86">
-        <v>-4.259924247983717</v>
+        <v>-4.009380385169992</v>
       </c>
       <c r="G86">
-        <v>2.0065767799581</v>
+        <v>2.625910328899415</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.016228773751248</v>
       </c>
       <c r="E87">
-        <v>-12.51402790576994</v>
+        <v>-12.71472987378989</v>
       </c>
       <c r="F87">
-        <v>-4.116957974669355</v>
+        <v>-3.989140056049989</v>
       </c>
       <c r="G87">
-        <v>3.658780673878789</v>
+        <v>2.525895437612493</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.048386725668062</v>
       </c>
       <c r="E88">
-        <v>-12.76401325641536</v>
+        <v>-14.33785722693715</v>
       </c>
       <c r="F88">
-        <v>-4.372206964330982</v>
+        <v>-3.722230138459155</v>
       </c>
       <c r="G88">
-        <v>3.538482070072753</v>
+        <v>3.118390393866936</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.189538520405551</v>
       </c>
       <c r="E89">
-        <v>-16.29003708690377</v>
+        <v>-15.41231466931507</v>
       </c>
       <c r="F89">
-        <v>-4.552747154668925</v>
+        <v>-4.243885398330712</v>
       </c>
       <c r="G89">
-        <v>3.771911946592303</v>
+        <v>2.561209026879899</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.438798254794468</v>
       </c>
       <c r="E90">
-        <v>-16.28492896822311</v>
+        <v>-16.11324999011832</v>
       </c>
       <c r="F90">
-        <v>-4.932584258446401</v>
+        <v>-3.80033690086912</v>
       </c>
       <c r="G90">
-        <v>3.074419728014336</v>
+        <v>2.942504419910997</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.78287837837081</v>
       </c>
       <c r="E91">
-        <v>-19.00862947335053</v>
+        <v>-19.11897479949544</v>
       </c>
       <c r="F91">
-        <v>-4.841474612914693</v>
+        <v>-4.27099206485252</v>
       </c>
       <c r="G91">
-        <v>3.958924664105733</v>
+        <v>2.894948433239366</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.221041558865368</v>
       </c>
       <c r="E92">
-        <v>-19.7003629349702</v>
+        <v>-20.98932060566944</v>
       </c>
       <c r="F92">
-        <v>-4.444057896115004</v>
+        <v>-3.889903297929414</v>
       </c>
       <c r="G92">
-        <v>3.217286320761584</v>
+        <v>2.466825373555277</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.745830723897475</v>
       </c>
       <c r="E93">
-        <v>-22.04888842551014</v>
+        <v>-23.30649999912829</v>
       </c>
       <c r="F93">
-        <v>-4.292604998758963</v>
+        <v>-3.952236288255271</v>
       </c>
       <c r="G93">
-        <v>2.539796418331893</v>
+        <v>2.705538880755504</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.337561829862796</v>
       </c>
       <c r="E94">
-        <v>-24.83375050058516</v>
+        <v>-24.80674721007742</v>
       </c>
       <c r="F94">
-        <v>-3.99735746068576</v>
+        <v>-4.119071139913897</v>
       </c>
       <c r="G94">
-        <v>1.584171032420332</v>
+        <v>2.350926484770932</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.990355263453564</v>
       </c>
       <c r="E95">
-        <v>-26.70751983310896</v>
+        <v>-26.7008720332657</v>
       </c>
       <c r="F95">
-        <v>-4.745988702393993</v>
+        <v>-4.534662237531006</v>
       </c>
       <c r="G95">
-        <v>1.993473640713665</v>
+        <v>1.694882296344639</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.696029123853577</v>
       </c>
       <c r="E96">
-        <v>-29.29066556198631</v>
+        <v>-28.19521864258283</v>
       </c>
       <c r="F96">
-        <v>-5.112441874044439</v>
+        <v>-4.416627337938702</v>
       </c>
       <c r="G96">
-        <v>1.083540404335126</v>
+        <v>1.93267216133941</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-6.424588801296456</v>
       </c>
       <c r="E97">
-        <v>-29.77648478200319</v>
+        <v>-31.2225216306065</v>
       </c>
       <c r="F97">
-        <v>-4.997385783632602</v>
+        <v>-4.463382879254914</v>
       </c>
       <c r="G97">
-        <v>0.1576602700939171</v>
+        <v>1.707449127211713</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.184044387892118</v>
       </c>
       <c r="E98">
-        <v>-35.08348951259823</v>
+        <v>-33.83178759756009</v>
       </c>
       <c r="F98">
-        <v>-4.696620490289352</v>
+        <v>-4.626109856963057</v>
       </c>
       <c r="G98">
-        <v>0.2828882762079283</v>
+        <v>0.3791953564908664</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.936302800589747</v>
       </c>
       <c r="E99">
-        <v>-35.45605612615729</v>
+        <v>-35.22722327760169</v>
       </c>
       <c r="F99">
-        <v>-5.280954169693734</v>
+        <v>-4.521526815624815</v>
       </c>
       <c r="G99">
-        <v>0.3236510234329744</v>
+        <v>1.074681384472036</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.697869399967441</v>
       </c>
       <c r="E100">
-        <v>-38.67637173333588</v>
+        <v>-38.607957812265</v>
       </c>
       <c r="F100">
-        <v>-5.071215685141913</v>
+        <v>-4.580575329198571</v>
       </c>
       <c r="G100">
-        <v>-0.8037817443301425</v>
+        <v>-0.4023913398756682</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.404080693446694</v>
       </c>
       <c r="E101">
-        <v>-41.88529143567416</v>
+        <v>-39.81631543833872</v>
       </c>
       <c r="F101">
-        <v>-5.019458461447598</v>
+        <v>-4.653641475962502</v>
       </c>
       <c r="G101">
-        <v>-0.4331496184810368</v>
+        <v>-0.1347767701176032</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.13878588767449</v>
       </c>
       <c r="E102">
-        <v>-43.43958145543083</v>
+        <v>-42.77529733900867</v>
       </c>
       <c r="F102">
-        <v>-5.503978010651653</v>
+        <v>-4.859470894740512</v>
       </c>
       <c r="G102">
-        <v>-1.690133964832453</v>
+        <v>-0.5050348043207713</v>
       </c>
     </row>
   </sheetData>
